--- a/src/assets/data/marketsense_input_data.xlsx
+++ b/src/assets/data/marketsense_input_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29622"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BN3PEPF00001EEE\EXCELCNV\f98f8320-fc76-467b-bb26-e9f1894ee6cc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MebrihitZere\A_project_workspace\marketsense\marketsense\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98867EDC-B3C5-4C77-B7E8-D62C323560D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AE6BA3-2D98-40E1-A7F5-244C4F353621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{73B66A8D-50AC-4252-8DA0-1C4CBF4D2D20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{73B66A8D-50AC-4252-8DA0-1C4CBF4D2D20}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,9 +757,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -797,7 +797,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -903,7 +903,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1045,7 +1045,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1054,7 +1054,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89101C9F-9BBB-4A60-925F-0F67AFD6A846}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1062,7 +1062,7 @@
     <col min="4" max="4" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>1.3560000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1129,10 +1129,10 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1157,10 +1157,10 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>10.68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>20.68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>-33.4</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>-19.11</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>-6.25</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>34.729999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>-14.56</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>95.73</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>-0.85</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>-2.25</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>45</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1647,10 +1647,10 @@
         <v>52</v>
       </c>
       <c r="D42">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>45</v>
       </c>

--- a/src/assets/data/marketsense_input_data.xlsx
+++ b/src/assets/data/marketsense_input_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MebrihitZere\A_project_workspace\marketsense\marketsense\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AE6BA3-2D98-40E1-A7F5-244C4F353621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1357BBA5-5234-4C72-BA42-48934B4298F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{73B66A8D-50AC-4252-8DA0-1C4CBF4D2D20}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{73B66A8D-50AC-4252-8DA0-1C4CBF4D2D20}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
